--- a/general/Strip_FP.xlsx
+++ b/general/Strip_FP.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guido\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guido\Desktop\Nuova cartella\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D078953-929E-4E30-A197-5D396C83379C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{093BA39A-50FF-4567-802E-97CF6F1463A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13550" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Polarimeters" sheetId="1" r:id="rId1"/>
@@ -1366,7 +1366,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1540,7 +1540,31 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1549,20 +1573,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1591,33 +1603,28 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="4" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -1677,8 +1684,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="8146534" y="0"/>
-          <a:ext cx="6760801" cy="6145376"/>
+          <a:off x="8193252" y="0"/>
+          <a:ext cx="6813869" cy="6181662"/>
           <a:chOff x="6136985" y="713668"/>
           <a:chExt cx="6730714" cy="6179655"/>
         </a:xfrm>
@@ -8179,8 +8186,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="4466770" y="272596"/>
-          <a:ext cx="6040406" cy="5629631"/>
+          <a:off x="4474368" y="275431"/>
+          <a:ext cx="6035303" cy="5632466"/>
           <a:chOff x="4696969" y="-6295"/>
           <a:chExt cx="6031315" cy="5620536"/>
         </a:xfrm>
@@ -11446,20 +11453,20 @@
       <c r="E1" s="21" t="s">
         <v>239</v>
       </c>
-      <c r="F1" s="71" t="s">
+      <c r="F1" s="89" t="s">
         <v>210</v>
       </c>
-      <c r="G1" s="72"/>
+      <c r="G1" s="90"/>
       <c r="H1" s="21" t="s">
         <v>59</v>
       </c>
       <c r="I1" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="J1" s="71" t="s">
+      <c r="J1" s="89" t="s">
         <v>211</v>
       </c>
-      <c r="K1" s="72"/>
+      <c r="K1" s="90"/>
       <c r="L1" s="21" t="s">
         <v>59</v>
       </c>
@@ -11476,7 +11483,7 @@
       <c r="T1" s="20"/>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A2" s="82" t="s">
+      <c r="A2" s="65" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="6" t="s">
@@ -11485,7 +11492,7 @@
       <c r="C2" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="D2" s="66">
+      <c r="D2" s="74">
         <v>1</v>
       </c>
       <c r="E2" s="6" t="s">
@@ -11507,20 +11514,20 @@
       </c>
       <c r="L2" s="50"/>
       <c r="M2" s="38"/>
-      <c r="N2" s="68" t="s">
+      <c r="N2" s="86" t="s">
         <v>208</v>
       </c>
       <c r="O2" s="9"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A3" s="82"/>
+      <c r="A3" s="65"/>
       <c r="B3" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="D3" s="66"/>
+      <c r="D3" s="74"/>
       <c r="E3" s="6" t="s">
         <v>39</v>
       </c>
@@ -11540,18 +11547,18 @@
       </c>
       <c r="L3" s="30"/>
       <c r="M3" s="33"/>
-      <c r="N3" s="69"/>
+      <c r="N3" s="87"/>
       <c r="O3" s="9"/>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" s="82"/>
+      <c r="A4" s="65"/>
       <c r="B4" s="6" t="s">
         <v>56</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="D4" s="66"/>
+      <c r="D4" s="74"/>
       <c r="E4" s="6" t="s">
         <v>40</v>
       </c>
@@ -11571,18 +11578,18 @@
       </c>
       <c r="L4" s="30"/>
       <c r="M4" s="33"/>
-      <c r="N4" s="69"/>
+      <c r="N4" s="87"/>
       <c r="O4" s="9"/>
     </row>
     <row r="5" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="83"/>
+      <c r="A5" s="66"/>
       <c r="B5" s="7" t="s">
         <v>19</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="D5" s="67"/>
+      <c r="D5" s="75"/>
       <c r="E5" s="7" t="s">
         <v>41</v>
       </c>
@@ -11602,11 +11609,11 @@
       </c>
       <c r="L5" s="31"/>
       <c r="M5" s="34"/>
-      <c r="N5" s="69"/>
+      <c r="N5" s="87"/>
       <c r="O5" s="9"/>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A6" s="84" t="s">
+      <c r="A6" s="67" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="6" t="s">
@@ -11615,7 +11622,7 @@
       <c r="C6" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="D6" s="65">
+      <c r="D6" s="76">
         <v>2</v>
       </c>
       <c r="E6" s="6" t="s">
@@ -11637,18 +11644,18 @@
       </c>
       <c r="L6" s="30"/>
       <c r="M6" s="33"/>
-      <c r="N6" s="69"/>
+      <c r="N6" s="87"/>
       <c r="O6" s="9"/>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A7" s="84"/>
+      <c r="A7" s="67"/>
       <c r="B7" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="D7" s="66"/>
+      <c r="D7" s="74"/>
       <c r="E7" s="6" t="s">
         <v>33</v>
       </c>
@@ -11668,18 +11675,18 @@
       </c>
       <c r="L7" s="50"/>
       <c r="M7" s="38"/>
-      <c r="N7" s="69"/>
+      <c r="N7" s="87"/>
       <c r="O7" s="9"/>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A8" s="84"/>
+      <c r="A8" s="67"/>
       <c r="B8" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="D8" s="66"/>
+      <c r="D8" s="74"/>
       <c r="E8" s="6" t="s">
         <v>34</v>
       </c>
@@ -11699,18 +11706,18 @@
       </c>
       <c r="L8" s="30"/>
       <c r="M8" s="33"/>
-      <c r="N8" s="69"/>
+      <c r="N8" s="87"/>
       <c r="O8" s="9"/>
     </row>
     <row r="9" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="85"/>
+      <c r="A9" s="68"/>
       <c r="B9" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D9" s="67"/>
+      <c r="D9" s="75"/>
       <c r="E9" s="7" t="s">
         <v>35</v>
       </c>
@@ -11730,11 +11737,11 @@
       </c>
       <c r="L9" s="31"/>
       <c r="M9" s="34"/>
-      <c r="N9" s="69"/>
+      <c r="N9" s="87"/>
       <c r="O9" s="9"/>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A10" s="86" t="s">
+      <c r="A10" s="69" t="s">
         <v>4</v>
       </c>
       <c r="B10" s="5" t="s">
@@ -11743,7 +11750,7 @@
       <c r="C10" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D10" s="65">
+      <c r="D10" s="76">
         <v>3</v>
       </c>
       <c r="E10" s="5" t="s">
@@ -11765,18 +11772,18 @@
       </c>
       <c r="L10" s="50"/>
       <c r="M10" s="38"/>
-      <c r="N10" s="69"/>
+      <c r="N10" s="87"/>
       <c r="O10" s="9"/>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A11" s="87"/>
+      <c r="A11" s="70"/>
       <c r="B11" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="D11" s="66"/>
+      <c r="D11" s="74"/>
       <c r="E11" s="6" t="s">
         <v>123</v>
       </c>
@@ -11796,21 +11803,21 @@
       </c>
       <c r="L11" s="30"/>
       <c r="M11" s="33"/>
-      <c r="N11" s="69"/>
+      <c r="N11" s="87"/>
       <c r="O11" s="9"/>
       <c r="Q11" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A12" s="87"/>
+      <c r="A12" s="70"/>
       <c r="B12" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="D12" s="66"/>
+      <c r="D12" s="74"/>
       <c r="E12" s="6" t="s">
         <v>124</v>
       </c>
@@ -11830,18 +11837,18 @@
       </c>
       <c r="L12" s="30"/>
       <c r="M12" s="33"/>
-      <c r="N12" s="69"/>
+      <c r="N12" s="87"/>
       <c r="O12" s="9"/>
     </row>
     <row r="13" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="87"/>
+      <c r="A13" s="70"/>
       <c r="B13" s="6" t="s">
         <v>16</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="D13" s="66"/>
+      <c r="D13" s="74"/>
       <c r="E13" s="6" t="s">
         <v>37</v>
       </c>
@@ -11861,11 +11868,11 @@
       </c>
       <c r="L13" s="30"/>
       <c r="M13" s="33"/>
-      <c r="N13" s="70"/>
+      <c r="N13" s="88"/>
       <c r="O13" s="9"/>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A14" s="88" t="s">
+      <c r="A14" s="71" t="s">
         <v>8</v>
       </c>
       <c r="B14" s="5" t="s">
@@ -11874,7 +11881,7 @@
       <c r="C14" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="D14" s="65">
+      <c r="D14" s="76">
         <v>4</v>
       </c>
       <c r="E14" s="5" t="s">
@@ -11896,19 +11903,19 @@
       </c>
       <c r="L14" s="32"/>
       <c r="M14" s="35"/>
-      <c r="N14" s="69" t="s">
+      <c r="N14" s="87" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A15" s="89"/>
+      <c r="A15" s="72"/>
       <c r="B15" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>203</v>
       </c>
-      <c r="D15" s="66"/>
+      <c r="D15" s="74"/>
       <c r="E15" s="6" t="s">
         <v>138</v>
       </c>
@@ -11928,17 +11935,17 @@
       </c>
       <c r="L15" s="30"/>
       <c r="M15" s="36"/>
-      <c r="N15" s="69"/>
+      <c r="N15" s="87"/>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A16" s="89"/>
+      <c r="A16" s="72"/>
       <c r="B16" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="D16" s="66"/>
+      <c r="D16" s="74"/>
       <c r="E16" s="6" t="s">
         <v>53</v>
       </c>
@@ -11958,17 +11965,17 @@
       </c>
       <c r="L16" s="50"/>
       <c r="M16" s="39"/>
-      <c r="N16" s="69"/>
+      <c r="N16" s="87"/>
     </row>
     <row r="17" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="90"/>
+      <c r="A17" s="73"/>
       <c r="B17" s="7" t="s">
         <v>31</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="D17" s="67"/>
+      <c r="D17" s="75"/>
       <c r="E17" s="7" t="s">
         <v>54</v>
       </c>
@@ -11988,10 +11995,10 @@
       </c>
       <c r="L17" s="31"/>
       <c r="M17" s="37"/>
-      <c r="N17" s="69"/>
+      <c r="N17" s="87"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="73" t="s">
+      <c r="A18" s="77" t="s">
         <v>7</v>
       </c>
       <c r="B18" s="5" t="s">
@@ -12000,7 +12007,7 @@
       <c r="C18" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D18" s="65">
+      <c r="D18" s="76">
         <v>5</v>
       </c>
       <c r="E18" s="5" t="s">
@@ -12022,17 +12029,17 @@
       </c>
       <c r="L18" s="32"/>
       <c r="M18" s="35"/>
-      <c r="N18" s="69"/>
+      <c r="N18" s="87"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="74"/>
+      <c r="A19" s="78"/>
       <c r="B19" s="6" t="s">
         <v>28</v>
       </c>
       <c r="C19" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="D19" s="66"/>
+      <c r="D19" s="74"/>
       <c r="E19" s="6" t="s">
         <v>50</v>
       </c>
@@ -12052,17 +12059,17 @@
       </c>
       <c r="L19" s="30"/>
       <c r="M19" s="36"/>
-      <c r="N19" s="69"/>
+      <c r="N19" s="87"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="74"/>
+      <c r="A20" s="78"/>
       <c r="B20" s="6" t="s">
         <v>121</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="D20" s="66"/>
+      <c r="D20" s="74"/>
       <c r="E20" s="6" t="s">
         <v>122</v>
       </c>
@@ -12082,17 +12089,17 @@
       </c>
       <c r="L20" s="50"/>
       <c r="M20" s="39"/>
-      <c r="N20" s="69"/>
+      <c r="N20" s="87"/>
     </row>
     <row r="21" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="75"/>
+      <c r="A21" s="79"/>
       <c r="B21" s="7" t="s">
         <v>23</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="D21" s="67"/>
+      <c r="D21" s="75"/>
       <c r="E21" s="7" t="s">
         <v>51</v>
       </c>
@@ -12112,10 +12119,10 @@
       </c>
       <c r="L21" s="31"/>
       <c r="M21" s="37"/>
-      <c r="N21" s="69"/>
+      <c r="N21" s="87"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="76" t="s">
+      <c r="A22" s="80" t="s">
         <v>97</v>
       </c>
       <c r="B22" s="5" t="s">
@@ -12124,7 +12131,7 @@
       <c r="C22" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="D22" s="65">
+      <c r="D22" s="76">
         <v>6</v>
       </c>
       <c r="E22" s="5" t="s">
@@ -12146,17 +12153,17 @@
       </c>
       <c r="L22" s="32"/>
       <c r="M22" s="35"/>
-      <c r="N22" s="69"/>
+      <c r="N22" s="87"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="77"/>
+      <c r="A23" s="81"/>
       <c r="B23" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C23" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="D23" s="66"/>
+      <c r="D23" s="74"/>
       <c r="E23" s="6" t="s">
         <v>43</v>
       </c>
@@ -12176,17 +12183,17 @@
       </c>
       <c r="L23" s="30"/>
       <c r="M23" s="36"/>
-      <c r="N23" s="69"/>
+      <c r="N23" s="87"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="77"/>
+      <c r="A24" s="81"/>
       <c r="B24" s="6" t="s">
         <v>55</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="D24" s="66"/>
+      <c r="D24" s="74"/>
       <c r="E24" s="6" t="s">
         <v>44</v>
       </c>
@@ -12206,17 +12213,17 @@
       </c>
       <c r="L24" s="30"/>
       <c r="M24" s="36"/>
-      <c r="N24" s="69"/>
+      <c r="N24" s="87"/>
     </row>
     <row r="25" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="78"/>
+      <c r="A25" s="82"/>
       <c r="B25" s="7" t="s">
         <v>22</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D25" s="67"/>
+      <c r="D25" s="75"/>
       <c r="E25" s="7" t="s">
         <v>45</v>
       </c>
@@ -12236,10 +12243,10 @@
       </c>
       <c r="L25" s="51"/>
       <c r="M25" s="40"/>
-      <c r="N25" s="69"/>
+      <c r="N25" s="87"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="79" t="s">
+      <c r="A26" s="83" t="s">
         <v>6</v>
       </c>
       <c r="B26" s="5" t="s">
@@ -12248,7 +12255,7 @@
       <c r="C26" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="D26" s="65">
+      <c r="D26" s="76">
         <v>7</v>
       </c>
       <c r="E26" s="5" t="s">
@@ -12270,17 +12277,17 @@
       </c>
       <c r="L26" s="32"/>
       <c r="M26" s="35"/>
-      <c r="N26" s="69"/>
+      <c r="N26" s="87"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="80"/>
+      <c r="A27" s="84"/>
       <c r="B27" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C27" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="D27" s="66"/>
+      <c r="D27" s="74"/>
       <c r="E27" s="6" t="s">
         <v>47</v>
       </c>
@@ -12300,17 +12307,17 @@
       </c>
       <c r="L27" s="30"/>
       <c r="M27" s="36"/>
-      <c r="N27" s="69"/>
+      <c r="N27" s="87"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="80"/>
+      <c r="A28" s="84"/>
       <c r="B28" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C28" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="D28" s="66"/>
+      <c r="D28" s="74"/>
       <c r="E28" s="6" t="s">
         <v>110</v>
       </c>
@@ -12330,17 +12337,17 @@
       </c>
       <c r="L28" s="30"/>
       <c r="M28" s="36"/>
-      <c r="N28" s="69"/>
+      <c r="N28" s="87"/>
     </row>
     <row r="29" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="81"/>
+      <c r="A29" s="85"/>
       <c r="B29" s="7" t="s">
         <v>26</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D29" s="67"/>
+      <c r="D29" s="75"/>
       <c r="E29" s="7" t="s">
         <v>48</v>
       </c>
@@ -12356,28 +12363,28 @@
       <c r="K29" s="12"/>
       <c r="L29" s="1"/>
       <c r="M29" s="4"/>
-      <c r="N29" s="70"/>
+      <c r="N29" s="88"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="N2:N13"/>
+    <mergeCell ref="N14:N29"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="D18:D21"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="D22:D25"/>
+    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="D26:D29"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="A6:A9"/>
     <mergeCell ref="A10:A13"/>
     <mergeCell ref="A14:A17"/>
     <mergeCell ref="D2:D5"/>
     <mergeCell ref="D6:D9"/>
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="D18:D21"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="D22:D25"/>
-    <mergeCell ref="A26:A29"/>
-    <mergeCell ref="D26:D29"/>
     <mergeCell ref="D10:D13"/>
     <mergeCell ref="D14:D17"/>
-    <mergeCell ref="N2:N13"/>
-    <mergeCell ref="N14:N29"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="J1:K1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -12661,11 +12668,11 @@
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="62" t="s">
+      <c r="A24" s="91" t="s">
         <v>254</v>
       </c>
-      <c r="B24" s="63"/>
-      <c r="C24" s="64" t="s">
+      <c r="B24" s="92"/>
+      <c r="C24" s="93" t="s">
         <v>260</v>
       </c>
     </row>
